--- a/Result/profitability/6776.xlsx
+++ b/Result/profitability/6776.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3871,45 +3871,45 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6417</v>
+        <v>9107</v>
       </c>
       <c r="D28" t="n">
-        <v>6031</v>
+        <v>8387</v>
       </c>
       <c r="E28" t="n">
-        <v>386</v>
+        <v>719</v>
       </c>
       <c r="F28" t="n">
-        <v>6.01</v>
+        <v>7.9</v>
       </c>
       <c r="G28" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>-16</v>
       </c>
       <c r="J28" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K28" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="M28" t="n">
-        <v>1.10625</v>
+        <v>1.105</v>
       </c>
       <c r="N28" t="n">
-        <v>6.55125</v>
+        <v>6.7875</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3933,28 +3933,28 @@
         <v>114.2</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01000000000000001</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.00990099009900991</v>
+        <v>-0.01980198019801982</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.46</v>
+        <v>1.430000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.07109737248840808</v>
+        <v>0.2210200927357033</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.02000000000000002</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.01960784313725494</v>
+        <v>-0.02941176470588236</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.7800000000000002</v>
+        <v>1.11</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.1148748159057438</v>
+        <v>0.1634756995581739</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3963,17 +3963,17 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率衰退</t>
+          <t>EPS衰退 / 毛利率成長</t>
         </is>
       </c>
       <c r="AK28" t="n">
@@ -3998,42 +3998,42 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8333</v>
+        <v>5644</v>
       </c>
       <c r="D29" t="n">
-        <v>7891</v>
+        <v>5535</v>
       </c>
       <c r="E29" t="n">
-        <v>442</v>
+        <v>109</v>
       </c>
       <c r="F29" t="n">
-        <v>5.31</v>
+        <v>1.93</v>
       </c>
       <c r="G29" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-10</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="K29" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M29" t="n">
         <v>1.09875</v>
       </c>
       <c r="N29" t="n">
-        <v>6.3425</v>
+        <v>6.15625</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -4060,28 +4060,28 @@
         <v>114.3</v>
       </c>
       <c r="W29" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.1919191919191918</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-5.970000000000001</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-0.7556962025316456</v>
+      </c>
+      <c r="AA29" t="n">
         <v>0.1699999999999999</v>
       </c>
-      <c r="X29" t="n">
-        <v>0.1699999999999999</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>-0.7000000000000002</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>-0.1164725457570716</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.1599999999999999</v>
-      </c>
       <c r="AB29" t="n">
-        <v>0.1584158415841583</v>
+        <v>0.1683168316831682</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.74</v>
+        <v>-5.12</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.2468085106382979</v>
+        <v>-0.726241134751773</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4160,7 +4160,7 @@
         <v>1.04375</v>
       </c>
       <c r="N30" t="n">
-        <v>6.29</v>
+        <v>6.10375</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -4187,16 +4187,16 @@
         <v>114.4</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.1299999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.1025641025641024</v>
+        <v>-0.1101694915254237</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.9000000000000004</v>
+        <v>4.28</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.1694915254237288</v>
+        <v>2.217616580310881</v>
       </c>
       <c r="AA30" t="n">
         <v>0.03000000000000003</v>
@@ -4287,7 +4287,7 @@
         <v>1.0525</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2075</v>
+        <v>6.021249999999999</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -4365,6 +4365,133 @@
       </c>
       <c r="AM31" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11092</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10113</v>
+      </c>
+      <c r="E32" t="n">
+        <v>980</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="G32" t="n">
+        <v>216</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J32" t="n">
+        <v>197</v>
+      </c>
+      <c r="K32" t="n">
+        <v>115</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.08125</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6.276249999999999</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.09649122807017552</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.4105431309904155</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2626262626262625</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.9299999999999997</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.1177215189873417</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
